--- a/csv/model/market share limits/formula_market share limits_QC.xlsx
+++ b/csv/model/market share limits/formula_market share limits_QC.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
+  <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="3624" yWindow="2148" windowWidth="17280" windowHeight="8880" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1" iterate="1" calcCompleted="0" calcOnSave="0"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1" calcOnSave="0"/>
 </workbook>
 </file>
 
@@ -440,12 +440,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
+  <sheetPr codeName="Sheet1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:X272"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
       <c r="B1" t="inlineStr">
@@ -587,7 +587,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -662,7 +662,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -812,7 +812,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1262,7 +1262,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1712,7 +1712,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1862,7 +1862,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Market share new_min</t>
+          <t>market_share_new_min</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2012,7 +2012,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2087,7 +2087,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Market share new_min</t>
+          <t>market_share_new_min</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2237,7 +2237,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2312,7 +2312,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2387,7 +2387,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2462,7 +2462,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2762,7 +2762,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2912,7 +2912,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2987,7 +2987,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -3062,7 +3062,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -3212,7 +3212,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -3287,7 +3287,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -3362,7 +3362,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3437,7 +3437,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3512,7 +3512,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3587,7 +3587,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3662,7 +3662,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3737,7 +3737,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3812,7 +3812,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3887,7 +3887,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3962,7 +3962,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -4037,7 +4037,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -4112,7 +4112,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -4187,7 +4187,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -4262,7 +4262,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -4337,7 +4337,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -4487,7 +4487,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -4562,7 +4562,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -4637,7 +4637,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -4787,7 +4787,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -4862,7 +4862,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4937,7 +4937,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -5012,7 +5012,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -5162,7 +5162,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -5237,7 +5237,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Market share new_min</t>
+          <t>market_share_new_min</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -5312,7 +5312,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -5387,7 +5387,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -5462,7 +5462,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -5537,7 +5537,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -5687,7 +5687,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -5762,7 +5762,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -5837,7 +5837,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -5912,7 +5912,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -5987,7 +5987,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -6062,7 +6062,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -6137,7 +6137,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -6212,7 +6212,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -6287,7 +6287,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -6362,7 +6362,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -6437,7 +6437,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -6512,7 +6512,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -6587,7 +6587,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -6662,7 +6662,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -6737,7 +6737,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -6812,7 +6812,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -6887,7 +6887,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -6962,7 +6962,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -7037,7 +7037,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -7112,7 +7112,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -7187,7 +7187,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -7262,7 +7262,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Market share new_min</t>
+          <t>market_share_new_min</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -7337,7 +7337,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Market share new_min</t>
+          <t>market_share_new_min</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -7412,7 +7412,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -7487,7 +7487,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -7562,7 +7562,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -7637,7 +7637,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -7712,7 +7712,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -7787,7 +7787,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -7862,7 +7862,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -7937,7 +7937,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -8012,7 +8012,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -8087,7 +8087,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -8162,7 +8162,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -8237,7 +8237,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -8312,7 +8312,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -8387,7 +8387,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -8462,7 +8462,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -8537,7 +8537,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -8612,7 +8612,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -8687,7 +8687,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -8762,7 +8762,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -8837,7 +8837,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -8912,7 +8912,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -8987,7 +8987,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -9062,7 +9062,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -9137,7 +9137,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -9212,7 +9212,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -9287,7 +9287,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -9362,7 +9362,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Market share new_min</t>
+          <t>market_share_new_min</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -9437,7 +9437,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -9512,7 +9512,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Market share new_min</t>
+          <t>market_share_new_min</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -9587,7 +9587,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -9662,7 +9662,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Market share new_min</t>
+          <t>market_share_new_min</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -9737,7 +9737,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -9812,7 +9812,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Market share new_min</t>
+          <t>market_share_new_min</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -9887,7 +9887,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -9962,7 +9962,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Market share new_min</t>
+          <t>market_share_new_min</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -10037,7 +10037,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -10112,7 +10112,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Market share new_min</t>
+          <t>market_share_new_min</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -10187,7 +10187,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -10262,7 +10262,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -10337,7 +10337,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
@@ -10412,7 +10412,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
@@ -10487,7 +10487,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
@@ -10562,7 +10562,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -10637,7 +10637,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
@@ -10712,7 +10712,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
@@ -10787,7 +10787,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
@@ -10862,7 +10862,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
@@ -10937,7 +10937,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
@@ -11012,7 +11012,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
@@ -11087,7 +11087,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
@@ -11162,7 +11162,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
@@ -11237,7 +11237,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
@@ -11312,7 +11312,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
@@ -11387,7 +11387,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
@@ -11462,7 +11462,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
@@ -11537,7 +11537,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
@@ -11612,7 +11612,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
@@ -11687,7 +11687,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
@@ -11762,7 +11762,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
@@ -11837,7 +11837,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
@@ -11912,7 +11912,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
@@ -11987,7 +11987,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
@@ -12062,7 +12062,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
@@ -12137,7 +12137,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
@@ -12212,7 +12212,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
@@ -12287,7 +12287,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
@@ -12362,7 +12362,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
@@ -12437,7 +12437,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
@@ -12512,7 +12512,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
@@ -12587,7 +12587,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
@@ -12662,7 +12662,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
@@ -12737,7 +12737,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
@@ -12812,7 +12812,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
@@ -12887,7 +12887,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
@@ -12962,7 +12962,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
@@ -13037,7 +13037,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
@@ -13112,7 +13112,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
@@ -13187,7 +13187,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
@@ -13262,7 +13262,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
@@ -13337,7 +13337,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Market share new_min</t>
+          <t>market_share_new_min</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
@@ -13412,7 +13412,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
@@ -13487,7 +13487,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Market share new_min</t>
+          <t>market_share_new_min</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
@@ -13562,7 +13562,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
@@ -13637,7 +13637,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Market share new_min</t>
+          <t>market_share_new_min</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
@@ -13712,7 +13712,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
@@ -13787,7 +13787,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
@@ -13862,7 +13862,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
@@ -13937,7 +13937,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
@@ -14012,7 +14012,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
@@ -14087,7 +14087,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
@@ -14162,7 +14162,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
@@ -14237,7 +14237,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Market share new_min</t>
+          <t>market_share_new_min</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
@@ -14312,7 +14312,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
@@ -14387,7 +14387,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Market share new_min</t>
+          <t>market_share_new_min</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
@@ -14462,7 +14462,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
@@ -14537,7 +14537,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Market share new_min</t>
+          <t>market_share_new_min</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
@@ -14612,7 +14612,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
@@ -14687,7 +14687,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Market share new_min</t>
+          <t>market_share_new_min</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
@@ -14762,7 +14762,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L192" t="inlineStr">
@@ -14837,7 +14837,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
@@ -14912,7 +14912,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Market share new_min</t>
+          <t>market_share_new_min</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
@@ -14987,7 +14987,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
@@ -15062,7 +15062,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
@@ -15137,7 +15137,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">
@@ -15212,7 +15212,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
@@ -15287,7 +15287,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">
@@ -15362,7 +15362,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
@@ -15437,7 +15437,7 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L201" t="inlineStr">
@@ -15527,7 +15527,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L202" t="inlineStr">
@@ -15602,7 +15602,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L203" t="inlineStr">
@@ -15677,7 +15677,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L204" t="inlineStr">
@@ -15752,7 +15752,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L205" t="inlineStr">
@@ -15827,7 +15827,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L206" t="inlineStr">
@@ -15902,7 +15902,7 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L207" t="inlineStr">
@@ -15977,7 +15977,7 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L208" t="inlineStr">
@@ -16052,7 +16052,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L209" t="inlineStr">
@@ -16127,7 +16127,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L210" t="inlineStr">
@@ -16202,7 +16202,7 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L211" t="inlineStr">
@@ -16277,7 +16277,7 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L212" t="inlineStr">
@@ -16352,7 +16352,7 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L213" t="inlineStr">
@@ -16427,7 +16427,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Market share new_min</t>
+          <t>market_share_new_min</t>
         </is>
       </c>
       <c r="L214" t="inlineStr">
@@ -16502,7 +16502,7 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L215" t="inlineStr">
@@ -16577,7 +16577,7 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Market share new_min</t>
+          <t>market_share_new_min</t>
         </is>
       </c>
       <c r="L216" t="inlineStr">
@@ -16652,7 +16652,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L217" t="inlineStr">
@@ -16727,7 +16727,7 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Market share new_min</t>
+          <t>market_share_new_min</t>
         </is>
       </c>
       <c r="L218" t="inlineStr">
@@ -16802,7 +16802,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L219" t="inlineStr">
@@ -16877,7 +16877,7 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Market share new_min</t>
+          <t>market_share_new_min</t>
         </is>
       </c>
       <c r="L220" t="inlineStr">
@@ -16952,7 +16952,7 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L221" t="inlineStr">
@@ -17027,7 +17027,7 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L222" t="inlineStr">
@@ -17102,7 +17102,7 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Market share new_min</t>
+          <t>market_share_new_min</t>
         </is>
       </c>
       <c r="L223" t="inlineStr">
@@ -17177,7 +17177,7 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L224" t="inlineStr">
@@ -17252,7 +17252,7 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Market share new_min</t>
+          <t>market_share_new_min</t>
         </is>
       </c>
       <c r="L225" t="inlineStr">
@@ -17327,7 +17327,7 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L226" t="inlineStr">
@@ -17412,7 +17412,7 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L227" t="inlineStr">
@@ -17497,7 +17497,7 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L228" t="inlineStr">
@@ -17582,7 +17582,7 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L229" t="inlineStr">
@@ -17667,7 +17667,7 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L230" t="inlineStr">
@@ -17752,7 +17752,7 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L231" t="inlineStr">
@@ -17837,7 +17837,7 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L232" t="inlineStr">
@@ -17922,7 +17922,7 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L233" t="inlineStr">
@@ -18007,7 +18007,7 @@
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L234" t="inlineStr">
@@ -18092,7 +18092,7 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L235" t="inlineStr">
@@ -18177,7 +18177,7 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L236" t="inlineStr">
@@ -18262,7 +18262,7 @@
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L237" t="inlineStr">
@@ -18347,7 +18347,7 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Market share new_min</t>
+          <t>market_share_new_min</t>
         </is>
       </c>
       <c r="L238" t="inlineStr">
@@ -18432,7 +18432,7 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Market share new_min</t>
+          <t>market_share_new_min</t>
         </is>
       </c>
       <c r="L239" t="inlineStr">
@@ -18517,7 +18517,7 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Market share new_min</t>
+          <t>market_share_new_min</t>
         </is>
       </c>
       <c r="L240" t="inlineStr">
@@ -18602,7 +18602,7 @@
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Market share new_min</t>
+          <t>market_share_new_min</t>
         </is>
       </c>
       <c r="L241" t="inlineStr">
@@ -18687,7 +18687,7 @@
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Market share new_min</t>
+          <t>market_share_new_min</t>
         </is>
       </c>
       <c r="L242" t="inlineStr">
@@ -18772,7 +18772,7 @@
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Market share new_min</t>
+          <t>market_share_new_min</t>
         </is>
       </c>
       <c r="L243" t="inlineStr">
@@ -18857,7 +18857,7 @@
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Market share new_min</t>
+          <t>market_share_new_min</t>
         </is>
       </c>
       <c r="L244" t="inlineStr">
@@ -18942,7 +18942,7 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Market share new_min</t>
+          <t>market_share_new_min</t>
         </is>
       </c>
       <c r="L245" t="inlineStr">
@@ -19027,7 +19027,7 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Market share new_min</t>
+          <t>market_share_new_min</t>
         </is>
       </c>
       <c r="L246" t="inlineStr">
@@ -19112,7 +19112,7 @@
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Market share new_min</t>
+          <t>market_share_new_min</t>
         </is>
       </c>
       <c r="L247" t="inlineStr">
@@ -19197,7 +19197,7 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Market share new_min</t>
+          <t>market_share_new_min</t>
         </is>
       </c>
       <c r="L248" t="inlineStr">
@@ -19282,7 +19282,7 @@
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Market share new_min</t>
+          <t>market_share_new_min</t>
         </is>
       </c>
       <c r="L249" t="inlineStr">
@@ -19367,7 +19367,7 @@
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L250" t="inlineStr">
@@ -19457,7 +19457,7 @@
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L251" t="inlineStr">
@@ -19532,7 +19532,7 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L252" t="inlineStr">
@@ -19607,7 +19607,7 @@
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L253" t="inlineStr">
@@ -19687,7 +19687,7 @@
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L254" t="inlineStr">
@@ -19767,7 +19767,7 @@
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L255" t="inlineStr">
@@ -19847,7 +19847,7 @@
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L256" t="inlineStr">
@@ -19927,7 +19927,7 @@
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L257" t="inlineStr">
@@ -20007,7 +20007,7 @@
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L258" t="inlineStr">
@@ -20087,7 +20087,7 @@
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L259" t="inlineStr">
@@ -20167,7 +20167,7 @@
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L260" t="inlineStr">
@@ -20247,7 +20247,7 @@
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L261" t="inlineStr">
@@ -20327,7 +20327,7 @@
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L262" t="inlineStr">
@@ -20407,7 +20407,7 @@
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L263" t="inlineStr">
@@ -20487,7 +20487,7 @@
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L264" t="inlineStr">
@@ -20567,7 +20567,7 @@
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L265" t="inlineStr">
@@ -20647,7 +20647,7 @@
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L266" t="inlineStr">
@@ -20727,7 +20727,7 @@
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L267" t="inlineStr">
@@ -20807,7 +20807,7 @@
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L268" t="inlineStr">
@@ -20887,7 +20887,7 @@
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L269" t="inlineStr">
@@ -20967,7 +20967,7 @@
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L270" t="inlineStr">
@@ -21047,7 +21047,7 @@
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L271" t="inlineStr">
@@ -21127,7 +21127,7 @@
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L272" t="inlineStr">
